--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>132024704</v>
       </c>
       <c r="B4" t="n">
-        <v>93203</v>
+        <v>93206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>132051094</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>132071946</v>
       </c>
       <c r="B6" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>132072630</v>
       </c>
       <c r="B7" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>132024756</v>
       </c>
       <c r="B3" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>132024704</v>
       </c>
       <c r="B4" t="n">
-        <v>93206</v>
+        <v>93212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>132051094</v>
       </c>
       <c r="B5" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>132071946</v>
       </c>
       <c r="B6" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>132072630</v>
       </c>
       <c r="B7" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>132024756</v>
       </c>
       <c r="B3" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>132024704</v>
       </c>
       <c r="B4" t="n">
-        <v>93212</v>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>132051094</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>132071946</v>
       </c>
       <c r="B6" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>132072630</v>
       </c>
       <c r="B7" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>132024704</v>
       </c>
       <c r="B4" t="n">
-        <v>93222</v>
+        <v>93223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>132051094</v>
       </c>
       <c r="B5" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>132071946</v>
       </c>
       <c r="B6" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>132072630</v>
       </c>
       <c r="B7" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>132071946</v>
       </c>
       <c r="B6" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>132072630</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11734-2026 artfynd.xlsx
+++ b/artfynd/A 11734-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>128526680</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132024756</v>
+        <v>132025397</v>
       </c>
       <c r="B3" t="n">
-        <v>57132</v>
+        <v>92910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -818,9 +818,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403234</v>
+        <v>403166</v>
       </c>
       <c r="R3" t="n">
-        <v>6633013</v>
+        <v>6633060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,37 +890,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132024704</v>
+        <v>132051094</v>
       </c>
       <c r="B4" t="n">
-        <v>93223</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403269</v>
+        <v>403142</v>
       </c>
       <c r="R4" t="n">
-        <v>6633004</v>
+        <v>6633132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,37 +1000,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132051094</v>
+        <v>132024704</v>
       </c>
       <c r="B5" t="n">
-        <v>91872</v>
+        <v>93297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403142</v>
+        <v>403269</v>
       </c>
       <c r="R5" t="n">
-        <v>6633132</v>
+        <v>6633004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,17 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,38 +1105,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132071946</v>
+        <v>132025186</v>
       </c>
       <c r="B6" t="n">
-        <v>97987</v>
+        <v>93307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403270</v>
+        <v>403078</v>
       </c>
       <c r="R6" t="n">
-        <v>6633020</v>
+        <v>6633072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132072630</v>
+        <v>132024756</v>
       </c>
       <c r="B7" t="n">
-        <v>97984</v>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,38 +1221,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granskog, Vrm</t>
+          <t>Granskogen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403232</v>
+        <v>403234</v>
       </c>
       <c r="R7" t="n">
-        <v>6633039</v>
+        <v>6633013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,12 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,7 +1297,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,6 +1312,210 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132072630</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Granskog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>403232</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6633039</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Hult</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Hult</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132071946</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>403270</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6633020</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Hult</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Hult</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
